--- a/AAII_Financials/Yearly/WSTL_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/WSTL_YR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="124" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="121" uniqueCount="92">
   <si>
     <t>WSTL</t>
   </si>
@@ -2368,8 +2368,8 @@
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="D45" s="3" t="s">
-        <v>17</v>
+      <c r="D45" s="3">
+        <v>100</v>
       </c>
       <c r="E45" s="3">
         <v>100</v>
@@ -2470,8 +2470,8 @@
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="D47" s="3" t="s">
-        <v>17</v>
+      <c r="D47" s="3">
+        <v>0</v>
       </c>
       <c r="E47" s="3">
         <v>100</v>
@@ -2726,10 +2726,10 @@
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>100</v>
-      </c>
-      <c r="E52" s="3" t="s">
-        <v>17</v>
+        <v>0</v>
+      </c>
+      <c r="E52" s="3">
+        <v>0</v>
       </c>
       <c r="F52" s="3" t="s">
         <v>17</v>
@@ -2972,7 +2972,7 @@
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="E58" s="3">
         <v>400</v>
